--- a/Шаблон_промптов.xlsx
+++ b/Шаблон_промптов.xlsx
@@ -1,59 +1,214 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Промпты" sheetId="1" r:id="rId1"/>
-    <sheet name="Инструкция" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Промпты" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Инструкция" state="visible" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="39">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Промпт</t>
+  </si>
+  <si>
+    <t>Комментарий</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>A majestic snow leopard sitting on a mountain peak at golden hour, cinematic lighting, 8K</t>
+  </si>
+  <si>
+    <t>Главный кадр для обложки</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>Futuristic cityscape with neon lights reflecting in rain puddles, cyberpunk atmosphere</t>
+  </si>
+  <si>
+    <t>Неоновый город — вариант 1</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>Cozy reading nook with warm lamp light, scattered books, and a sleeping cat</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>Шаблон промптов — Mews Studio</t>
+  </si>
+  <si>
+    <t>Столбец</t>
+  </si>
+  <si>
+    <t>Описание</t>
+  </si>
+  <si>
+    <t>Порядковый номер (001, 002, ...). Можно оставить пустым — присвоится автоматически при импорте.</t>
+  </si>
+  <si>
+    <t>Текст для генерации изображения. Пишите на английском — модели лучше понимают English prompts.</t>
+  </si>
+  <si>
+    <t>Заметка для себя. Не влияет на генерацию. Пример: «для обложки», «вариант 2», «переделать».</t>
+  </si>
+  <si>
+    <t>Советы</t>
+  </si>
+  <si>
+    <t>• Чем подробнее промпт, тем точнее результат: стиль, освещение, ракурс, настроение.</t>
+  </si>
+  <si>
+    <t>• Сохраните файл как .xlsx или .csv и импортируйте через «Загрузить промпты».</t>
+  </si>
+  <si>
+    <t>• Минимально нужна только колонка «Промпт» — остальные колонки опциональны.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <color rgb="FF888888"/>
+      <sz val="10"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A84FF"/>
+      <sz val="10"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <color rgb="FF666666"/>
+      <sz val="10"/>
+      <name val="Inter"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A1A1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F8F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,18 +216,60 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF3A3A3A"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,192 +594,334 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Промпт</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Категория</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Стиль</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Комментарий</v>
-      </c>
-    </row>
-    <row r="2" xml:space="preserve">
-      <c r="A2" t="str">
-        <v>001</v>
-      </c>
-      <c r="B2" t="str" xml:space="preserve">
-        <v xml:space="preserve">A cinematic night scene above a ruined futuristic city, a red-and-gold cyber phoenix with glowing violet energy cores flying through storm clouds, ultra realistic, dramatic lighting, volumetric smoke, sharp metal reflections, epic composition.
-The mood should feel premium, dark, and emotionally powerful, like a high-budget sci-fi poster.</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Сцена</v>
-      </c>
-      <c r="D2" t="str">
-        <v>cinematic, ultra realistic, 8K</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Главная сцена серии</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>A close-up fashion portrait of a young woman in a silver futuristic jacket, soft studio lighting, natural skin texture, detailed eyes, premium editorial photography, clean dark background, high realism.</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Персонаж</v>
-      </c>
-      <c r="D3" t="str">
-        <v>editorial photography, portrait</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Персонаж для 3 эпизода</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>A magical enchanted forest with giant glowing mushrooms, floating fireflies, a small fairy sitting on a mossy stone, whimsical cartoon style, soft warm lighting, depth of field.</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Фон</v>
-      </c>
-      <c r="D4" t="str">
-        <v>cartoon, whimsical, magical</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Фон леса для серии про эльфов</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>YouTube thumbnail showing an epic dragon battle, text space on the right side, vibrant orange and blue contrast, bold dynamic composition, 16:9 landscape.</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Превью</v>
-      </c>
-      <c r="D5" t="str">
-        <v>YouTube thumbnail, bold, vibrant</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Превью для ютуба</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>005</v>
-      </c>
-      <c r="B6" t="str">
-        <v>A cute baby cat astronaut floating in space, wearing a tiny spacesuit, surrounded by colorful planets and stars, adorable cartoon style, soft pastel colors, kawaii aesthetic.</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Персонаж</v>
-      </c>
-      <c r="D6" t="str">
-        <v>cartoon, kawaii, pastel</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Котик-астронавт</v>
+    <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
-  </ignoredErrors>
+  <autoFilter ref="A1:C1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="15"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="85" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Что это</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Шаблон промптов для Higgsfield Studio. Заполните лист «Промпты» и загрузите файл в приложение.</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Необязательно. Уникальный номер промпта (001, 002...). Если не указан — присвоится автоматически.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Промпт</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Обязательно. Текст промпта для генерации. Можно писать длинные тексты с переносами строк внутри одной ячейки.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Категория</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Необязательно. Тип контента: Персонаж, Фон, Сцена, Превью и т.д. Помогает при отборе.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Стиль</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Необязательно. Стилевые теги (cinematic, cartoon, kawaii...). Хранятся как метаданные. Не добавляются к промпту при генерации.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Комментарий</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Необязательно. Заметки для себя. Приложение их не использует при генерации.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Важно</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Один промпт = одна строка. Не разбивайте промпт на несколько строк таблицы!</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Форматы</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Приложение поддерживает .xlsx, .xls и .csv файлы.</v>
+    <row r="1" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="6"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
-  </ignoredErrors>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>